--- a/UPMPackages/com.solotopia.nova.framework.besthttp/Nova/Tracks/Tracks.xlsx
+++ b/UPMPackages/com.solotopia.nova.framework.besthttp/Nova/Tracks/Tracks.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>每次物理发送开始时记录一次。</t>
+          <t>普通请求每次物理发送开始时记录；HostKey + NetCmd 业务请求链全程只记录一次。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>埋点契约版本，当前固定为 1。</t>
+          <t>埋点契约版本，当前固定为 2。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>每次物理发送开始时上报。</t>
+          <t>普通请求每次物理发送开始时上报；业务请求链首个候选开始时上报。</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>失败后重试会产生新的 attempt；扩展字段由 TelemetryContext 提供。</t>
+          <t>业务请求链固定为 1 attempt、0～N error、1 end，并通过 best_http_chain_id 聚合。</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>逻辑请求唯一 ID；同一请求的所有事件共用。</t>
+          <t>单个 HTTPRequest 的唯一 ID；业务请求链请使用 best_http_chain_id 聚合。</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -630,7 +630,7 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>best_http_correlation_id</t>
+          <t>best_http_chain_id</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>调用方可选关联 ID，例如业务 fallback 链 ID。</t>
+          <t>请求链关联 ID；Nova 业务主备/IP 轮换中的所有事件共用。</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>某个物理 attempt 以网络或协议异常失败。</t>
+          <t>某次物理发送以网络或协议异常失败；业务请求链可产生零到多条。</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>埋点契约版本，当前固定为 1。</t>
+          <t>埋点契约版本，当前固定为 2。</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>每个失败 attempt 完成时最多上报一次。</t>
+          <t>每个失败物理发送完成时最多上报一次。</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>不代表逻辑请求最终失败；HTTP 4xx/5xx 不上报本事件。</t>
+          <t>不代表整条请求链最终失败；HTTP 4xx/5xx 不上报本事件。</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>逻辑请求唯一 ID；同一请求的所有事件共用。</t>
+          <t>单个 HTTPRequest 的唯一 ID；业务请求链请使用 best_http_chain_id 聚合。</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -1028,7 +1028,7 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>best_http_correlation_id</t>
+          <t>best_http_chain_id</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>调用方可选关联 ID，例如业务 fallback 链 ID。</t>
+          <t>请求链关联 ID；Nova 业务主备/IP 轮换中的所有事件共用。</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BestHTTP 逻辑请求结束</t>
+          <t>BestHTTP 请求最终结束</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>逻辑 HTTPRequest 进入唯一终态。</t>
+          <t>普通请求按 HTTPRequest 收口；HostKey + NetCmd 业务请求链全程只记录一次最终结果。</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>埋点契约版本，当前固定为 1。</t>
+          <t>埋点契约版本，当前固定为 2。</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>逻辑请求终态确定后恰好上报一次。</t>
+          <t>普通请求终态或业务请求链最终结果确定后上报一次。</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>HTTP 4xx/5xx 以 result=http_error 记录；诊断字段按可用事实条件出现。</t>
+          <t>业务请求链通过 best_http_chain_id 聚合；HTTP 4xx/5xx 以 result=http_error 记录。</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>逻辑请求唯一 ID；同一请求的所有事件共用。</t>
+          <t>单个 HTTPRequest 的唯一 ID；业务请求链请使用 best_http_chain_id 聚合。</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2209,7 +2209,7 @@
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>best_http_correlation_id</t>
+          <t>best_http_chain_id</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>调用方可选关联 ID，例如业务 fallback 链 ID。</t>
+          <t>请求链关联 ID；Nova 业务主备/IP 轮换中的所有事件共用。</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>非首个 attempt 最终取得 2xx 时为 true。</t>
+          <t>先发生网络失败且最终 result=success 时为 true；最终失败时为 false。</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
